--- a/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gabin et maman sont au marché. Il y a un panier. Dedans, des oranges. Maman dit : on va compter des objets. Gabin touche une orange. Une. Il en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Gabin dit : cinq oranges. Maman sourit. Elle en pose encore. Six. Sept. Huit. Neuf. Dix. Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.</t>
+          <t>Gabin et maman sont au marché. Il y a un panier. Dedans, des oranges. On va compter des objets. Gabin touche une orange. Une. Il en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq oranges. Maman sourit. Elle en pose encore. Six. Sept. Huit. Neuf. Dix. Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin et maman sont au marché. Il y a un panier. Dedans, des oranges.
+maman|On va compter des objets.
+narrateur|Gabin touche une orange. Une. Il en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq.
+enfant-m|Cinq oranges. Maman sourit. Elle en pose encore. Six. Sept. Huit. Neuf. Dix.
+narrateur|Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin compte les oranges. Combien y en a-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1659,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin a compté des objets. Il a dit le nombre. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1822,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin pose le panier. Maman dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1989,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Gabin compte les oranges. Combien y en a-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1664,6 +1675,7 @@
           <t>narrateur|Gabin a compté des objets. Il a dit le nombre. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1839,7 @@
           <t>narrateur|Gabin pose le panier. Maman dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gabin compte les oranges</t>
+          <t>Raphaël compte les oranges</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une bâche claque au-dessus des caisses. Raphaël touche les oranges du panier. Il compte jusqu'à dix. Papa et maman disent le nombre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gabin et maman sont au marché. Il y a un panier. Dedans, des oranges. On va compter des objets. Gabin touche une orange. Une. Il en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Cinq oranges. Maman sourit. Elle en pose encore. Six. Sept. Huit. Neuf. Dix. Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.</t>
+          <t>Une bâche claque au-dessus des caisses. Le tissu est épais et un peu rêche. Ça sent l'écorce d'orange. Une caisse de bois repose à l'ombre. Le bois est clair et sec. Un sac en papier attend près des pieds. Le papier fait un petit bruit. Loin, une clochette de vélo tinte. Le sol est un peu poussiéreux. Raphaël, tu entends la bâche ? Oui, papa. Ça claque. Ça sent l'orange, ici. Le panier est prêt. En ce moment, Raphaël ouvre le panier. Dedans, des oranges. Elles sont lourdes et lisses. On compte des objets. On touche. On dit le nombre. Raphaël touche une orange. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu dis le nombre. Maman en pose encore. Les oranges roulent tout doux. Six. Sept. Huit. Neuf. Dix. Dix. Tu as compté des objets. Dix oranges. Bravo, Raphaël. Tu as fait du bon travail. Raphaël pose les oranges une à une. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont dans le panier. On peut les toucher. La bâche claque encore. Le sac en papier reste calme. Ça sent le jus, hein ? Oui. Le jus. On rentre avec le panier ? Oui, papa. Papa pose des citrons près du sac. Ils sont jaunes et bosselés. On compte aussi les citrons. Raphaël touche un citron. Un. Deux. Trois. Quatre. Cinq. Cinq citrons. Tu dis le nombre. Cinq. Tu as compté des objets. La bâche claque plus doux. Le bois de la caisse reste sec. Oranges et citrons. J'ai dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gabin et maman sont au marché. Il y a un panier. Dedans, des oranges.
-maman|On va compter des objets.
-narrateur|Gabin touche une orange. Une. Il en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq.
-enfant-m|Cinq oranges. Maman sourit. Elle en pose encore. Six. Sept. Huit. Neuf. Dix.
-narrateur|Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.</t>
+          <t>narrateur|Une bâche claque au-dessus des caisses.
+narrateur|Le tissu est épais et un peu rêche.
+narrateur|Ça sent l'écorce d'orange.
+narrateur|Une caisse de bois repose à l'ombre.
+narrateur|Le bois est clair et sec.
+narrateur|Un sac en papier attend près des pieds.
+narrateur|Le papier fait un petit bruit.
+narrateur|Loin, une clochette de vélo tinte.
+narrateur|Le sol est un peu poussiéreux.
+papa|Raphaël, tu entends la bâche ?
+enfant-m|Oui, papa.
+enfant-m|Ça claque.
+maman|Ça sent l'orange, ici.
+papa|Le panier est prêt.
+narrateur|En ce moment, Raphaël ouvre le panier.
+narrateur|Dedans, des oranges.
+narrateur|Elles sont lourdes et lisses.
+maman|On compte des objets.
+papa|On touche. On dit le nombre.
+narrateur|Raphaël touche une orange.
+enfant-m|Une.
+narrateur|Il en touche une autre.
+enfant-m|Deux.
+enfant-m|Trois.
+enfant-m|Quatre.
+enfant-m|Cinq.
+maman|Cinq oranges.
+papa|Tu dis le nombre.
+narrateur|Maman en pose encore.
+narrateur|Les oranges roulent tout doux.
+enfant-m|Six.
+enfant-m|Sept.
+enfant-m|Huit.
+enfant-m|Neuf.
+enfant-m|Dix.
+papa|Dix.
+maman|Tu as compté des objets.
+enfant-m|Dix oranges.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël pose les oranges une à une.
+narrateur|Une. Deux. Trois. Quatre. Cinq.
+narrateur|Six. Sept. Huit. Neuf. Dix.
+maman|Les objets sont dans le panier.
+papa|On peut les toucher.
+narrateur|La bâche claque encore.
+narrateur|Le sac en papier reste calme.
+maman|Ça sent le jus, hein ?
+enfant-m|Oui. Le jus.
+papa|On rentre avec le panier ?
+enfant-m|Oui, papa.
+narrateur|Papa pose des citrons près du sac.
+narrateur|Ils sont jaunes et bosselés.
+maman|On compte aussi les citrons.
+narrateur|Raphaël touche un citron.
+enfant-m|Un. Deux. Trois. Quatre. Cinq.
+papa|Cinq citrons.
+maman|Tu dis le nombre.
+enfant-m|Cinq.
+papa|Tu as compté des objets.
+narrateur|La bâche claque plus doux.
+narrateur|Le bois de la caisse reste sec.
+maman|Oranges et citrons.
+enfant-m|J'ai dit le nombre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gabin compte les oranges. Combien y en a-t-il ?</t>
+          <t>Raphaël compte les oranges. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1575,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gabin compte les oranges. Combien y en a-t-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël compte les oranges.
+narrateur|Combien y en a-t-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gabin a compté des objets. Il a dit le nombre. Maman était là.</t>
+          <t>Raphaël a compté des objets. Il a dit le nombre. Maman était là. Papa aussi. Tu as dit dix ? Oui, maman. Bravo, Raphaël. Tu as fait du bon travail. Le panier repose à l'ombre. Les oranges sentent le jus. Le panier est lourd ? Oui, un peu. Une orange brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1743,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gabin a compté des objets. Il a dit le nombre. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a compté des objets.
+narrateur|Il a dit le nombre.
+narrateur|Maman était là. Papa aussi.
+maman|Tu as dit dix ?
+enfant-m|Oui, maman.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Le panier repose à l'ombre.
+narrateur|Les oranges sentent le jus.
+maman|Le panier est lourd ?
+enfant-m|Oui, un peu.
+narrateur|Une orange brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gabin pose le panier. Maman dit merci.</t>
+          <t>Raphaël pose le panier. Je te tiens l'anse ? Oui, maman. Maman tient l'anse avec lui. L'anse est un peu rêche. Tu as fini de compter ? Oui, papa. Bravo. La bâche claque plus loin. On rentre ? Oui. Ça sent encore l'orange.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,10 +1917,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gabin pose le panier. Maman dit merci.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël pose le panier.
+maman|Je te tiens l'anse ?
+enfant-m|Oui, maman.
+narrateur|Maman tient l'anse avec lui.
+narrateur|L'anse est un peu rêche.
+papa|Tu as fini de compter ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|La bâche claque plus loin.
+maman|On rentre ?
+enfant-m|Oui.
+narrateur|Ça sent encore l'orange.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël tient le sac en papier. Les oranges sentent le jus. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,10 +2095,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël tient le sac en papier.
+narrateur|Les oranges sentent le jus.
+maman|Merci d'avoir compté.
+papa|On touche. On dit le nombre.
+enfant-m|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Raphaël compte les oranges</t>
+          <t>Le filet d'oranges de Raphaël</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une bâche claque au-dessus des caisses. Raphaël touche les oranges du panier. Il compte jusqu'à dix. Papa et maman disent le nombre.</t>
+          <t>Le store rayé fait une ombre. Raphaël touche les oranges du filet. Une à dix. Il dit le nombre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une bâche claque au-dessus des caisses. Le tissu est épais et un peu rêche. Ça sent l'écorce d'orange. Une caisse de bois repose à l'ombre. Le bois est clair et sec. Un sac en papier attend près des pieds. Le papier fait un petit bruit. Loin, une clochette de vélo tinte. Le sol est un peu poussiéreux. Raphaël, tu entends la bâche ? Oui, papa. Ça claque. Ça sent l'orange, ici. Le panier est prêt. En ce moment, Raphaël ouvre le panier. Dedans, des oranges. Elles sont lourdes et lisses. On compte des objets. On touche. On dit le nombre. Raphaël touche une orange. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu dis le nombre. Maman en pose encore. Les oranges roulent tout doux. Six. Sept. Huit. Neuf. Dix. Dix. Tu as compté des objets. Dix oranges. Bravo, Raphaël. Tu as fait du bon travail. Raphaël pose les oranges une à une. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont dans le panier. On peut les toucher. La bâche claque encore. Le sac en papier reste calme. Ça sent le jus, hein ? Oui. Le jus. On rentre avec le panier ? Oui, papa. Papa pose des citrons près du sac. Ils sont jaunes et bosselés. On compte aussi les citrons. Raphaël touche un citron. Un. Deux. Trois. Quatre. Cinq. Cinq citrons. Tu dis le nombre. Cinq. Tu as compté des objets. La bâche claque plus doux. Le bois de la caisse reste sec. Oranges et citrons. J'ai dit le nombre.</t>
+          <t>Le store rayé fait une ombre tiède. Les pavés sont chauds sous les sandales. Une cagette de bois sent l'orange. Le jus pique un peu le nez. Un filet vide pend au poignet de maman. Une balance fait tic, tout doux. Une feuille d'orange est tombée. Tu as senti, Raphaël ? Oui, maman. Ça sent l'orange. On prend un filet. En ce moment, Raphaël s'approche de la cagette. Dedans, des oranges. Elles sont rondes et brillantes. On va compter des objets. Des oranges. Des oranges. Raphaël touche une orange. La peau est un peu granuleuse. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu as dit le nombre. Cinq. Maman en pose encore dans le filet. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Raphaël. Tu as compté des objets. C'est du bon travail. Les oranges sentent le jus. Parce que tu comptes, tu sais le nombre. Dix. Oui. On pose les oranges ? Oui, maman. Raphaël pose les oranges. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. On peut les toucher. Ils sont dans le panier. Dans le filet. Oui. Le store rayé bouge un peu. Une ombre passe sur les oranges. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. La balance fait encore tic. Les pavés restent chauds. Le filet est lourd, un peu. Oui. On le porte à deux. Ils portent le filet. Les oranges se touchent. Ça fait un petit bruit mou. Tu as compté des objets. Dix oranges. Oui. Tu as dit le nombre. Le store rayé claque un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabin et maman sont au marché. Il y a un panier. Dedans, des oranges. Maman dit : on va &lt;emphasis level="moderate"&gt;compter&lt;/emphasis&gt; des objets. Gabin touche une orange. Une. Il en touche une autre. Deux. Encore une. Trois. Encore une. Quatre. Encore une. Cinq. Gabin dit : cinq oranges. Maman sourit. Elle en pose encore. Six. Sept. Huit. Neuf. Dix. Gabin répète : dix. Il a compté des objets. Les oranges sentent le jus. Parce qu'il compte, Gabin sait le nombre. Maman dit le nombre. Dix. Gabin pose les oranges. Une. Deux. Trois. Quatre. Cinq. Six. Sept. Huit. Neuf. Dix. Les objets sont là. Gabin les compte. Parce que les objets sont dans le panier, on peut les toucher.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le store rayé fait une ombre tiède. Les pavés sont chauds sous les sandales. Une cagette de bois sent l'orange. Le jus pique un peu le nez. Un filet vide pend au poignet de maman. Une balance fait tic, tout doux. Une feuille d'orange est tombée. Tu as senti, Raphaël ? Oui, maman. Ça sent l'orange. On prend un filet. En ce moment, Raphaël s'approche de la cagette. Dedans, des oranges. Elles sont rondes et brillantes. On va compter des objets. Des oranges. Des oranges. Raphaël touche une orange. La peau est un peu granuleuse. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu as dit le nombre. Cinq. Maman en pose encore dans le filet. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Raphaël. Tu as compté des objets. C'est du bon travail. Les oranges sentent le jus. Parce que tu comptes, tu sais le nombre. Dix. Oui. On pose les oranges ? Oui, maman. Raphaël pose les oranges. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. On peut les toucher. Ils sont dans le panier. Dans le filet. Oui. Le store rayé bouge un peu. Une ombre passe sur les oranges. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. La balance fait encore tic. Les pavés restent chauds. Le filet est lourd, un peu. Oui. On le porte à deux. Ils portent le filet. Les oranges se touchent. Ça fait un petit bruit mou. Tu as compté des objets. Dix oranges. Oui. Tu as dit le nombre. Le store rayé claque un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,70 +1324,82 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une bâche claque au-dessus des caisses.
-narrateur|Le tissu est épais et un peu rêche.
-narrateur|Ça sent l'écorce d'orange.
-narrateur|Une caisse de bois repose à l'ombre.
-narrateur|Le bois est clair et sec.
-narrateur|Un sac en papier attend près des pieds.
-narrateur|Le papier fait un petit bruit.
-narrateur|Loin, une clochette de vélo tinte.
-narrateur|Le sol est un peu poussiéreux.
-papa|Raphaël, tu entends la bâche ?
-enfant-m|Oui, papa.
-enfant-m|Ça claque.
-maman|Ça sent l'orange, ici.
-papa|Le panier est prêt.
-narrateur|En ce moment, Raphaël ouvre le panier.
+          <t>narrateur|Le store rayé fait une ombre tiède.
+narrateur|Les pavés sont chauds sous les sandales.
+narrateur|Une cagette de bois sent l'orange.
+narrateur|Le jus pique un peu le nez.
+narrateur|Un filet vide pend au poignet de maman.
+narrateur|Une balance fait tic, tout doux.
+narrateur|Une feuille d'orange est tombée.
+maman|Tu as senti, Raphaël ?
+enfant-m|Oui, maman.
+enfant-m|Ça sent l'orange.
+maman|On prend un filet.
+narrateur|En ce moment, Raphaël s'approche de la cagette.
 narrateur|Dedans, des oranges.
-narrateur|Elles sont lourdes et lisses.
-maman|On compte des objets.
-papa|On touche. On dit le nombre.
+narrateur|Elles sont rondes et brillantes.
+maman|On va compter des objets.
+maman|Des oranges.
+enfant-m|Des oranges.
 narrateur|Raphaël touche une orange.
+narrateur|La peau est un peu granuleuse.
+maman|Une.
 enfant-m|Une.
 narrateur|Il en touche une autre.
 enfant-m|Deux.
 enfant-m|Trois.
 enfant-m|Quatre.
 enfant-m|Cinq.
-maman|Cinq oranges.
-papa|Tu dis le nombre.
-narrateur|Maman en pose encore.
-narrateur|Les oranges roulent tout doux.
+enfant-m|Cinq oranges.
+maman|Tu as dit le nombre.
+maman|Cinq.
+narrateur|Maman en pose encore dans le filet.
+maman|On continue.
 enfant-m|Six.
 enfant-m|Sept.
 enfant-m|Huit.
 enfant-m|Neuf.
 enfant-m|Dix.
-papa|Dix.
+enfant-m|Dix.
+maman|Tu as dit le nombre.
+maman|Dix.
+maman|Bravo, Raphaël.
+maman|Tu as compté des objets.
+maman|C'est du bon travail.
+narrateur|Les oranges sentent le jus.
+maman|Parce que tu comptes, tu sais le nombre.
+enfant-m|Dix.
+maman|Oui.
+maman|On pose les oranges ?
+enfant-m|Oui, maman.
+narrateur|Raphaël pose les oranges.
+enfant-m|Une, deux, trois, quatre, cinq.
+enfant-m|Six, sept, huit, neuf, dix.
+maman|Les objets sont là.
+maman|On peut les toucher.
+maman|Ils sont dans le panier.
+enfant-m|Dans le filet.
+maman|Oui.
+narrateur|Le store rayé bouge un peu.
+narrateur|Une ombre passe sur les oranges.
+maman|Tu as fini de compter ?
+enfant-m|Oui, maman.
+enfant-m|Dix.
+maman|Bravo.
+maman|Tu as compté des objets.
+narrateur|La balance fait encore tic.
+narrateur|Les pavés restent chauds.
+enfant-m|Le filet est lourd, un peu.
+maman|Oui.
+maman|On le porte à deux.
+narrateur|Ils portent le filet.
+narrateur|Les oranges se touchent.
+narrateur|Ça fait un petit bruit mou.
 maman|Tu as compté des objets.
 enfant-m|Dix oranges.
-papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-narrateur|Raphaël pose les oranges une à une.
-narrateur|Une. Deux. Trois. Quatre. Cinq.
-narrateur|Six. Sept. Huit. Neuf. Dix.
-maman|Les objets sont dans le panier.
-papa|On peut les toucher.
-narrateur|La bâche claque encore.
-narrateur|Le sac en papier reste calme.
-maman|Ça sent le jus, hein ?
-enfant-m|Oui. Le jus.
-papa|On rentre avec le panier ?
-enfant-m|Oui, papa.
-narrateur|Papa pose des citrons près du sac.
-narrateur|Ils sont jaunes et bosselés.
-maman|On compte aussi les citrons.
-narrateur|Raphaël touche un citron.
-enfant-m|Un. Deux. Trois. Quatre. Cinq.
-papa|Cinq citrons.
-maman|Tu dis le nombre.
-enfant-m|Cinq.
-papa|Tu as compté des objets.
-narrateur|La bâche claque plus doux.
-narrateur|Le bois de la caisse reste sec.
-maman|Oranges et citrons.
-enfant-m|J'ai dit le nombre.</t>
+maman|Oui.
+maman|Tu as dit le nombre.
+narrateur|Le store rayé claque un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1424,7 +1436,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gabin compte les oranges. Combien y en a-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël compte les oranges. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1603,12 +1615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a compté des objets. Il a dit le nombre. Maman était là. Papa aussi. Tu as dit dix ? Oui, maman. Bravo, Raphaël. Tu as fait du bon travail. Le panier repose à l'ombre. Les oranges sentent le jus. Le panier est lourd ? Oui, un peu. Une orange brille encore.</t>
+          <t>Raphaël a compté des objets. Il a dit le nombre. Dix oranges. Bravo, Raphaël. Dix. Tu as fait du bon travail. Le filet penche un peu. Ça sent encore le jus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabin a compté des objets. Il a dit le nombre. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a compté des objets. Il a dit le nombre. Dix oranges. Bravo, Raphaël. Dix. Tu as fait du bon travail. Le filet penche un peu. Ça sent encore le jus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,16 +1757,12 @@
         <is>
           <t>narrateur|Raphaël a compté des objets.
 narrateur|Il a dit le nombre.
-narrateur|Maman était là. Papa aussi.
-maman|Tu as dit dix ?
-enfant-m|Oui, maman.
-papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-narrateur|Le panier repose à l'ombre.
-narrateur|Les oranges sentent le jus.
-maman|Le panier est lourd ?
-enfant-m|Oui, un peu.
-narrateur|Une orange brille encore.</t>
+maman|Dix oranges.
+maman|Bravo, Raphaël.
+enfant-m|Dix.
+maman|Tu as fait du bon travail.
+narrateur|Le filet penche un peu.
+narrateur|Ça sent encore le jus.</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le panier. Je te tiens l'anse ? Oui, maman. Maman tient l'anse avec lui. L'anse est un peu rêche. Tu as fini de compter ? Oui, papa. Bravo. La bâche claque plus loin. On rentre ? Oui. Ça sent encore l'orange.</t>
+          <t>Raphaël pose le filet. Merci, Raphaël. Merci, maman. Tu as fini de compter ? Oui. Dix. Bravo. Les pavés restent chauds. La feuille d'orange a bougé. On rentre avec le filet ? Oui, maman. Ils quittent l'ombre du store. Les pavés restent chauds. Tu as bien compté. Dix. Le filet tape contre la jambe. Ça sent encore l'orange.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabin pose le panier. Maman dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose le filet. Merci, Raphaël. Merci, maman. Tu as fini de compter ? Oui. Dix. Bravo. Les pavés restent chauds. La feuille d'orange a bougé. On rentre avec le filet ? Oui, maman. Ils quittent l'ombre du store. Les pavés restent chauds. Tu as bien compté. Dix. Le filet tape contre la jambe. Ça sent encore l'orange.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1917,17 +1925,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël pose le panier.
-maman|Je te tiens l'anse ?
+          <t>narrateur|Raphaël pose le filet.
+maman|Merci, Raphaël.
+enfant-m|Merci, maman.
+maman|Tu as fini de compter ?
+enfant-m|Oui.
+enfant-m|Dix.
+maman|Bravo.
+narrateur|Les pavés restent chauds.
+narrateur|La feuille d'orange a bougé.
+maman|On rentre avec le filet ?
 enfant-m|Oui, maman.
-narrateur|Maman tient l'anse avec lui.
-narrateur|L'anse est un peu rêche.
-papa|Tu as fini de compter ?
-enfant-m|Oui, papa.
-papa|Bravo.
-narrateur|La bâche claque plus loin.
-maman|On rentre ?
-enfant-m|Oui.
+narrateur|Ils quittent l'ombre du store.
+narrateur|Les pavés restent chauds.
+maman|Tu as bien compté.
+enfant-m|Dix.
+narrateur|Le filet tape contre la jambe.
 narrateur|Ça sent encore l'orange.</t>
         </is>
       </c>
@@ -1955,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël tient le sac en papier. Les oranges sentent le jus. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
+          <t>Le store rayé fait encore de l'ombre. Dix oranges. Tu as compté des objets. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le store rayé fait encore de l'ombre. Dix oranges. Tu as compté des objets. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,11 +2108,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël tient le sac en papier.
-narrateur|Les oranges sentent le jus.
-maman|Merci d'avoir compté.
-papa|On touche. On dit le nombre.
-enfant-m|Oui.
+          <t>narrateur|Le store rayé fait encore de l'ombre.
+enfant-m|Dix oranges.
+maman|Tu as compté des objets.
+maman|Bravo, Raphaël.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2121,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2178,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le store rayé fait une ombre tiède. Les pavés sont chauds sous les sandales. Une cagette de bois sent l'orange. Le jus pique un peu le nez. Un filet vide pend au poignet de maman. Une balance fait tic, tout doux. Une feuille d'orange est tombée. Tu as senti, Raphaël ? Oui, maman. Ça sent l'orange. On prend un filet. En ce moment, Raphaël s'approche de la cagette. Dedans, des oranges. Elles sont rondes et brillantes. On va compter des objets. Des oranges. Des oranges. Raphaël touche une orange. La peau est un peu granuleuse. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu as dit le nombre. Cinq. Maman en pose encore dans le filet. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Raphaël. Tu as compté des objets. C'est du bon travail. Les oranges sentent le jus. Parce que tu comptes, tu sais le nombre. Dix. Oui. On pose les oranges ? Oui, maman. Raphaël pose les oranges. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. On peut les toucher. Ils sont dans le panier. Dans le filet. Oui. Le store rayé bouge un peu. Une ombre passe sur les oranges. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. La balance fait encore tic. Les pavés restent chauds. Le filet est lourd, un peu. Oui. On le porte à deux. Ils portent le filet. Les oranges se touchent. Ça fait un petit bruit mou. Tu as compté des objets. Dix oranges. Oui. Tu as dit le nombre. Le store rayé claque un peu.</t>
+          <t>Le store rayé fait une ombre tiède. Les pavés sont chauds sous les sandales. Une cagette de bois sent l'orange. Le jus pique un peu le nez. Un filet vide pend au poignet de maman. Une balance fait tic, tout doux. Une feuille d'orange est tombée. Tu as senti, Raphaël ? Oui, maman. Ça sent l'orange. On prend un filet. En ce moment, Raphaël s'approche de la cagette. Dedans, des oranges. Elles sont rondes et brillantes. On va compter des objets. Des oranges. Des oranges. Raphaël touche une orange. La peau est un peu granuleuse. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu as dit le nombre. Cinq. Maman en pose encore dans le filet. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Raphaël. Tu as compté des objets. Les oranges sentent le jus. Parce que tu comptes, tu sais le nombre. Dix. Oui. On pose les oranges ? Oui, maman. Raphaël pose les oranges. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. On peut les toucher. Ils sont dans le panier. Dans le filet. Oui. Le store rayé bouge un peu. Une ombre passe sur les oranges. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. La balance fait encore tic. Les pavés restent chauds. Le filet est lourd, un peu. Oui. On le porte à deux. Ils portent le filet. Les oranges se touchent. Ça fait un petit bruit mou. Tu as compté des objets. Dix oranges. Oui. Tu as dit le nombre. Le store rayé claque un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le store rayé fait une ombre tiède. Les pavés sont chauds sous les sandales. Une cagette de bois sent l'orange. Le jus pique un peu le nez. Un filet vide pend au poignet de maman. Une balance fait tic, tout doux. Une feuille d'orange est tombée. Tu as senti, Raphaël ? Oui, maman. Ça sent l'orange. On prend un filet. En ce moment, Raphaël s'approche de la cagette. Dedans, des oranges. Elles sont rondes et brillantes. On va compter des objets. Des oranges. Des oranges. Raphaël touche une orange. La peau est un peu granuleuse. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu as dit le nombre. Cinq. Maman en pose encore dans le filet. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Raphaël. Tu as compté des objets. C'est du bon travail. Les oranges sentent le jus. Parce que tu comptes, tu sais le nombre. Dix. Oui. On pose les oranges ? Oui, maman. Raphaël pose les oranges. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. On peut les toucher. Ils sont dans le panier. Dans le filet. Oui. Le store rayé bouge un peu. Une ombre passe sur les oranges. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. La balance fait encore tic. Les pavés restent chauds. Le filet est lourd, un peu. Oui. On le porte à deux. Ils portent le filet. Les oranges se touchent. Ça fait un petit bruit mou. Tu as compté des objets. Dix oranges. Oui. Tu as dit le nombre. Le store rayé claque un peu.</t>
+          <t>Le store rayé fait une ombre tiède. Les pavés sont chauds sous les sandales. Une cagette de bois sent l'orange. Le jus pique un peu le nez. Un filet vide pend au poignet de maman. Une balance fait tic, tout doux. Une feuille d'orange est tombée. Tu as senti, Raphaël ? Oui, maman. Ça sent l'orange. On prend un filet. En ce moment, Raphaël s'approche de la cagette. Dedans, des oranges. Elles sont rondes et brillantes. On va compter des objets. Des oranges. Des oranges. Raphaël touche une orange. La peau est un peu granuleuse. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq oranges. Tu as dit le nombre. Cinq. Maman en pose encore dans le filet. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Raphaël. Tu as compté des objets. Les oranges sentent le jus. Parce que tu comptes, tu sais le nombre. Dix. Oui. On pose les oranges ? Oui, maman. Raphaël pose les oranges. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. On peut les toucher. Ils sont dans le panier. Dans le filet. Oui. Le store rayé bouge un peu. Une ombre passe sur les oranges. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. La balance fait encore tic. Les pavés restent chauds. Le filet est lourd, un peu. Oui. On le porte à deux. Ils portent le filet. Les oranges se touchent. Ça fait un petit bruit mou. Tu as compté des objets. Dix oranges. Oui. Tu as dit le nombre. Le store rayé claque un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 maman|Dix.
 maman|Bravo, Raphaël.
 maman|Tu as compté des objets.
-maman|C'est du bon travail.
 narrateur|Les oranges sentent le jus.
 maman|Parce que tu comptes, tu sais le nombre.
 enfant-m|Dix.
@@ -1615,12 +1614,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a compté des objets. Il a dit le nombre. Dix oranges. Bravo, Raphaël. Dix. Tu as fait du bon travail. Le filet penche un peu. Ça sent encore le jus.</t>
+          <t>Raphaël a compté des objets. Il a dit le nombre. Dix oranges. Bravo, Raphaël. Dix. Le filet penche un peu. Ça sent encore le jus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a compté des objets. Il a dit le nombre. Dix oranges. Bravo, Raphaël. Dix. Tu as fait du bon travail. Le filet penche un peu. Ça sent encore le jus.</t>
+          <t>Raphaël a compté des objets. Il a dit le nombre. Dix oranges. Bravo, Raphaël. Dix. Le filet penche un peu. Ça sent encore le jus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1760,7 +1759,6 @@
 maman|Dix oranges.
 maman|Bravo, Raphaël.
 enfant-m|Dix.
-maman|Tu as fait du bon travail.
 narrateur|Le filet penche un peu.
 narrateur|Ça sent encore le jus.</t>
         </is>
@@ -1968,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le store rayé fait encore de l'ombre. Dix oranges. Tu as compté des objets. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Le store rayé fait encore de l'ombre. Dix oranges. Tu as compté des objets. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le store rayé fait encore de l'ombre. Dix oranges. Tu as compté des objets. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Le store rayé fait encore de l'ombre. Dix oranges. Tu as compté des objets. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,8 +2109,7 @@
           <t>narrateur|Le store rayé fait encore de l'ombre.
 enfant-m|Dix oranges.
 maman|Tu as compté des objets.
-maman|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Raphaël.</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2180,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>marché, sous le store</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gabin, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
